--- a/Res_ConvLSTM/DroughtDataset_model_testing_1753344963_individual_h_8.xlsx
+++ b/Res_ConvLSTM/DroughtDataset_model_testing_1753344963_individual_h_8.xlsx
@@ -658,7 +658,7 @@
         <v>0.008471483344799909</v>
       </c>
       <c r="C2" t="n">
-        <v>50771040</v>
+        <v>6346380</v>
       </c>
       <c r="D2" t="n">
         <v>0</v>
@@ -679,49 +679,49 @@
         <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>50771040</v>
+        <v>6346380</v>
       </c>
       <c r="K2" t="n">
-        <v>35933069</v>
+        <v>4077420</v>
       </c>
       <c r="L2" t="n">
-        <v>20098731</v>
+        <v>1994767</v>
       </c>
       <c r="M2" t="n">
-        <v>4844558</v>
+        <v>390292</v>
       </c>
       <c r="N2" t="n">
-        <v>246209</v>
+        <v>14070</v>
       </c>
       <c r="O2" t="n">
-        <v>2877835</v>
+        <v>223975</v>
       </c>
       <c r="P2" t="n">
-        <v>1133453</v>
+        <v>86982</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.9999878406524658</v>
+        <v>0.9999916553497314</v>
       </c>
       <c r="R2" t="n">
-        <v>0.8740277290344238</v>
+        <v>0.7813187837600708</v>
       </c>
       <c r="S2" t="n">
-        <v>0.7571187019348145</v>
+        <v>0.5946244597434998</v>
       </c>
       <c r="T2" t="n">
-        <v>0.7022144794464111</v>
+        <v>0.5011962056159973</v>
       </c>
       <c r="U2" t="n">
-        <v>0.3062217235565186</v>
+        <v>0.07894515246152878</v>
       </c>
       <c r="V2" t="n">
-        <v>0.7501118779182434</v>
+        <v>0.5434914231300354</v>
       </c>
       <c r="W2" t="n">
-        <v>0.8343906998634338</v>
+        <v>0.6837562322616577</v>
       </c>
       <c r="X2" t="n">
-        <v>50771040</v>
+        <v>6346380</v>
       </c>
       <c r="Y2" t="n">
         <v>0</v>
@@ -742,46 +742,46 @@
         <v>0</v>
       </c>
       <c r="AE2" t="n">
-        <v>50771040</v>
+        <v>6346380</v>
       </c>
       <c r="AF2" t="n">
-        <v>38712019</v>
+        <v>4813274</v>
       </c>
       <c r="AG2" t="n">
-        <v>23936510</v>
+        <v>3010697</v>
       </c>
       <c r="AH2" t="n">
-        <v>6414507</v>
+        <v>804213</v>
       </c>
       <c r="AI2" t="n">
-        <v>473159</v>
+        <v>59267</v>
       </c>
       <c r="AJ2" t="n">
-        <v>3676427</v>
+        <v>460431</v>
       </c>
       <c r="AK2" t="n">
-        <v>1440753</v>
+        <v>180245</v>
       </c>
       <c r="AL2" t="n">
         <v>1</v>
       </c>
       <c r="AM2" t="n">
-        <v>0.9563227891921997</v>
+        <v>0.9555724859237671</v>
       </c>
       <c r="AN2" t="n">
-        <v>0.9114070534706116</v>
+        <v>0.9118132591247559</v>
       </c>
       <c r="AO2" t="n">
-        <v>0.8580120801925659</v>
+        <v>0.8582125902175903</v>
       </c>
       <c r="AP2" t="n">
-        <v>0.6619145274162292</v>
+        <v>0.6612037420272827</v>
       </c>
       <c r="AQ2" t="n">
-        <v>0.9019697904586792</v>
+        <v>0.9019888043403625</v>
       </c>
       <c r="AR2" t="n">
-        <v>0.9314440488815308</v>
+        <v>0.9314650297164917</v>
       </c>
     </row>
     <row r="3">
@@ -792,130 +792,130 @@
         <v>0.002029531499543211</v>
       </c>
       <c r="C3" t="n">
-        <v>23</v>
+        <v>4</v>
       </c>
       <c r="D3" t="n">
-        <v>35933069</v>
+        <v>4077420</v>
       </c>
       <c r="E3" t="n">
-        <v>4373317</v>
+        <v>914945</v>
       </c>
       <c r="F3" t="n">
-        <v>103622</v>
+        <v>29268</v>
       </c>
       <c r="G3" t="n">
-        <v>11569</v>
+        <v>3682</v>
       </c>
       <c r="H3" t="n">
-        <v>5729</v>
+        <v>1622</v>
       </c>
       <c r="I3" t="n">
-        <v>318</v>
+        <v>98</v>
       </c>
       <c r="J3" t="n">
-        <v>80556344</v>
+        <v>10069567</v>
       </c>
       <c r="K3" t="n">
-        <v>85721374</v>
+        <v>10247743</v>
       </c>
       <c r="L3" t="n">
-        <v>98574249</v>
+        <v>11746593</v>
       </c>
       <c r="M3" t="n">
-        <v>121791271</v>
+        <v>15088794</v>
       </c>
       <c r="N3" t="n">
-        <v>130054694</v>
+        <v>16162071</v>
       </c>
       <c r="O3" t="n">
-        <v>126291052</v>
+        <v>15716938</v>
       </c>
       <c r="P3" t="n">
-        <v>129555911</v>
+        <v>16182180</v>
       </c>
       <c r="Q3" t="n">
         <v>1</v>
       </c>
       <c r="R3" t="n">
-        <v>0.8888241648674011</v>
+        <v>0.8110977411270142</v>
       </c>
       <c r="S3" t="n">
-        <v>0.7640318870544434</v>
+        <v>0.6027384400367737</v>
       </c>
       <c r="T3" t="n">
-        <v>0.6474677920341492</v>
+        <v>0.4157451689243317</v>
       </c>
       <c r="U3" t="n">
-        <v>0.3441109955310822</v>
+        <v>0.1567268967628479</v>
       </c>
       <c r="V3" t="n">
-        <v>0.7056557536125183</v>
+        <v>0.438364714384079</v>
       </c>
       <c r="W3" t="n">
-        <v>0.7326202988624573</v>
+        <v>0.4493103921413422</v>
       </c>
       <c r="X3" t="n">
         <v>0</v>
       </c>
       <c r="Y3" t="n">
-        <v>38712019</v>
+        <v>4813274</v>
       </c>
       <c r="Z3" t="n">
-        <v>1591784</v>
+        <v>198388</v>
       </c>
       <c r="AA3" t="n">
-        <v>68580</v>
+        <v>8469</v>
       </c>
       <c r="AB3" t="n">
-        <v>54698</v>
+        <v>6867</v>
       </c>
       <c r="AC3" t="n">
-        <v>326</v>
+        <v>11</v>
       </c>
       <c r="AD3" t="n">
-        <v>240</v>
+        <v>30</v>
       </c>
       <c r="AE3" t="n">
-        <v>80556960</v>
+        <v>10069620</v>
       </c>
       <c r="AF3" t="n">
-        <v>89132297</v>
+        <v>11165177</v>
       </c>
       <c r="AG3" t="n">
-        <v>102695121</v>
+        <v>12815311</v>
       </c>
       <c r="AH3" t="n">
-        <v>122784182</v>
+        <v>15344357</v>
       </c>
       <c r="AI3" t="n">
-        <v>130370832</v>
+        <v>16295858</v>
       </c>
       <c r="AJ3" t="n">
-        <v>126850187</v>
+        <v>15855036</v>
       </c>
       <c r="AK3" t="n">
-        <v>129674836</v>
+        <v>16209148</v>
       </c>
       <c r="AL3" t="n">
         <v>1</v>
       </c>
       <c r="AM3" t="n">
-        <v>0.9575629830360413</v>
+        <v>0.9574769735336304</v>
       </c>
       <c r="AN3" t="n">
-        <v>0.9099209904670715</v>
+        <v>0.9097115993499756</v>
       </c>
       <c r="AO3" t="n">
-        <v>0.8572890758514404</v>
+        <v>0.8566603064537048</v>
       </c>
       <c r="AP3" t="n">
-        <v>0.6613048911094666</v>
+        <v>0.6601800322532654</v>
       </c>
       <c r="AQ3" t="n">
-        <v>0.9014734625816345</v>
+        <v>0.9011573195457458</v>
       </c>
       <c r="AR3" t="n">
-        <v>0.9312471747398376</v>
+        <v>0.9310656785964966</v>
       </c>
     </row>
     <row r="4">
@@ -926,285 +926,285 @@
         <v>0.03203123381705863</v>
       </c>
       <c r="C4" t="n">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="D4" t="n">
-        <v>4861909</v>
+        <v>1056966</v>
       </c>
       <c r="E4" t="n">
-        <v>20098731</v>
+        <v>1994767</v>
       </c>
       <c r="F4" t="n">
-        <v>1159505</v>
+        <v>205688</v>
       </c>
       <c r="G4" t="n">
-        <v>72855</v>
+        <v>24219</v>
       </c>
       <c r="H4" t="n">
-        <v>103407</v>
+        <v>25039</v>
       </c>
       <c r="I4" t="n">
-        <v>9721</v>
+        <v>2826</v>
       </c>
       <c r="J4" t="n">
-        <v>616</v>
+        <v>53</v>
       </c>
       <c r="K4" t="n">
-        <v>5178979</v>
+        <v>1141218</v>
       </c>
       <c r="L4" t="n">
-        <v>6447610</v>
+        <v>1359900</v>
       </c>
       <c r="M4" t="n">
-        <v>2054414</v>
+        <v>388429</v>
       </c>
       <c r="N4" t="n">
-        <v>557813</v>
+        <v>164155</v>
       </c>
       <c r="O4" t="n">
-        <v>958706</v>
+        <v>188129</v>
       </c>
       <c r="P4" t="n">
-        <v>224967</v>
+        <v>40230</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.9999939203262329</v>
+        <v>0.9999958276748657</v>
       </c>
       <c r="R4" t="n">
-        <v>0.8813638091087341</v>
+        <v>0.7959297895431519</v>
       </c>
       <c r="S4" t="n">
-        <v>0.760559618473053</v>
+        <v>0.5986539721488953</v>
       </c>
       <c r="T4" t="n">
-        <v>0.673730731010437</v>
+        <v>0.4544890224933624</v>
       </c>
       <c r="U4" t="n">
-        <v>0.3240626454353333</v>
+        <v>0.1050003916025162</v>
       </c>
       <c r="V4" t="n">
-        <v>0.7272050380706787</v>
+        <v>0.4853001832962036</v>
       </c>
       <c r="W4" t="n">
-        <v>0.7802007794380188</v>
+        <v>0.5422784090042114</v>
       </c>
       <c r="X4" t="n">
         <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>1650806</v>
+        <v>208961</v>
       </c>
       <c r="Z4" t="n">
-        <v>23936510</v>
+        <v>3010697</v>
       </c>
       <c r="AA4" t="n">
-        <v>664902</v>
+        <v>83070</v>
       </c>
       <c r="AB4" t="n">
-        <v>44224</v>
+        <v>5580</v>
       </c>
       <c r="AC4" t="n">
-        <v>9155</v>
+        <v>1131</v>
       </c>
       <c r="AD4" t="n">
-        <v>544</v>
+        <v>68</v>
       </c>
       <c r="AE4" t="n">
         <v>0</v>
       </c>
       <c r="AF4" t="n">
-        <v>1768056</v>
+        <v>223784</v>
       </c>
       <c r="AG4" t="n">
-        <v>2326738</v>
+        <v>291182</v>
       </c>
       <c r="AH4" t="n">
-        <v>1061503</v>
+        <v>132866</v>
       </c>
       <c r="AI4" t="n">
-        <v>241675</v>
+        <v>30368</v>
       </c>
       <c r="AJ4" t="n">
-        <v>399571</v>
+        <v>50031</v>
       </c>
       <c r="AK4" t="n">
-        <v>106042</v>
+        <v>13262</v>
       </c>
       <c r="AL4" t="n">
         <v>1</v>
       </c>
       <c r="AM4" t="n">
-        <v>0.9569424390792847</v>
+        <v>0.9565237760543823</v>
       </c>
       <c r="AN4" t="n">
-        <v>0.910663366317749</v>
+        <v>0.9107611775398254</v>
       </c>
       <c r="AO4" t="n">
-        <v>0.8576504588127136</v>
+        <v>0.8574357628822327</v>
       </c>
       <c r="AP4" t="n">
-        <v>0.6616095304489136</v>
+        <v>0.660691499710083</v>
       </c>
       <c r="AQ4" t="n">
-        <v>0.9017215967178345</v>
+        <v>0.9015728235244751</v>
       </c>
       <c r="AR4" t="n">
-        <v>0.9313456416130066</v>
+        <v>0.9312652945518494</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr"/>
       <c r="B5" t="inlineStr"/>
       <c r="C5" t="n">
-        <v>37</v>
+        <v>10</v>
       </c>
       <c r="D5" t="n">
-        <v>217206</v>
+        <v>61719</v>
       </c>
       <c r="E5" t="n">
-        <v>1751157</v>
+        <v>355700</v>
       </c>
       <c r="F5" t="n">
-        <v>4844558</v>
+        <v>390292</v>
       </c>
       <c r="G5" t="n">
-        <v>189078</v>
+        <v>48735</v>
       </c>
       <c r="H5" t="n">
-        <v>438727</v>
+        <v>72295</v>
       </c>
       <c r="I5" t="n">
-        <v>41552</v>
+        <v>10026</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>4494578</v>
+        <v>949619</v>
       </c>
       <c r="L5" t="n">
-        <v>6207410</v>
+        <v>1314740</v>
       </c>
       <c r="M5" t="n">
-        <v>2637757</v>
+        <v>548485</v>
       </c>
       <c r="N5" t="n">
-        <v>469284</v>
+        <v>75704</v>
       </c>
       <c r="O5" t="n">
-        <v>1200407</v>
+        <v>286958</v>
       </c>
       <c r="P5" t="n">
-        <v>413669</v>
+        <v>106608</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.9999952912330627</v>
+        <v>0.9999967813491821</v>
       </c>
       <c r="R5" t="n">
-        <v>0.9263404607772827</v>
+        <v>0.8726341724395752</v>
       </c>
       <c r="S5" t="n">
-        <v>0.9036380648612976</v>
+        <v>0.8370711207389832</v>
       </c>
       <c r="T5" t="n">
-        <v>0.9642713665962219</v>
+        <v>0.9429267644882202</v>
       </c>
       <c r="U5" t="n">
-        <v>0.9921791553497314</v>
+        <v>0.9853886961936951</v>
       </c>
       <c r="V5" t="n">
-        <v>0.9835593700408936</v>
+        <v>0.9710595011711121</v>
       </c>
       <c r="W5" t="n">
-        <v>0.995137095451355</v>
+        <v>0.9910551905632019</v>
       </c>
       <c r="X5" t="n">
         <v>0</v>
       </c>
       <c r="Y5" t="n">
-        <v>64693</v>
+        <v>8176</v>
       </c>
       <c r="Z5" t="n">
-        <v>684803</v>
+        <v>86508</v>
       </c>
       <c r="AA5" t="n">
-        <v>6414507</v>
+        <v>804213</v>
       </c>
       <c r="AB5" t="n">
-        <v>79806</v>
+        <v>10008</v>
       </c>
       <c r="AC5" t="n">
-        <v>233442</v>
+        <v>29239</v>
       </c>
       <c r="AD5" t="n">
-        <v>5064</v>
+        <v>633</v>
       </c>
       <c r="AE5" t="n">
         <v>0</v>
       </c>
       <c r="AF5" t="n">
-        <v>1715628</v>
+        <v>213765</v>
       </c>
       <c r="AG5" t="n">
-        <v>2369631</v>
+        <v>298810</v>
       </c>
       <c r="AH5" t="n">
-        <v>1067808</v>
+        <v>134564</v>
       </c>
       <c r="AI5" t="n">
-        <v>242334</v>
+        <v>30507</v>
       </c>
       <c r="AJ5" t="n">
-        <v>401815</v>
+        <v>50502</v>
       </c>
       <c r="AK5" t="n">
-        <v>106369</v>
+        <v>13345</v>
       </c>
       <c r="AL5" t="n">
         <v>1</v>
       </c>
       <c r="AM5" t="n">
-        <v>0.9734734296798706</v>
+        <v>0.9733461737632751</v>
       </c>
       <c r="AN5" t="n">
-        <v>0.9642394185066223</v>
+        <v>0.9640599489212036</v>
       </c>
       <c r="AO5" t="n">
-        <v>0.9837862849235535</v>
+        <v>0.9837091565132141</v>
       </c>
       <c r="AP5" t="n">
-        <v>0.996314525604248</v>
+        <v>0.9962917566299438</v>
       </c>
       <c r="AQ5" t="n">
-        <v>0.9938978552818298</v>
+        <v>0.9938759207725525</v>
       </c>
       <c r="AR5" t="n">
-        <v>0.998382568359375</v>
+        <v>0.9983792304992676</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr"/>
       <c r="B6" t="inlineStr"/>
       <c r="C6" t="n">
-        <v>92</v>
+        <v>10</v>
       </c>
       <c r="D6" t="n">
-        <v>89752</v>
+        <v>17171</v>
       </c>
       <c r="E6" t="n">
-        <v>129517</v>
+        <v>24608</v>
       </c>
       <c r="F6" t="n">
-        <v>175562</v>
+        <v>24238</v>
       </c>
       <c r="G6" t="n">
-        <v>246209</v>
+        <v>14070</v>
       </c>
       <c r="H6" t="n">
-        <v>67301</v>
+        <v>8459</v>
       </c>
       <c r="I6" t="n">
-        <v>7060</v>
+        <v>1218</v>
       </c>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
@@ -1224,22 +1224,22 @@
         <v>0</v>
       </c>
       <c r="Y6" t="n">
-        <v>52110</v>
+        <v>6591</v>
       </c>
       <c r="Z6" t="n">
-        <v>43017</v>
+        <v>5395</v>
       </c>
       <c r="AA6" t="n">
-        <v>87434</v>
+        <v>11026</v>
       </c>
       <c r="AB6" t="n">
-        <v>473159</v>
+        <v>59267</v>
       </c>
       <c r="AC6" t="n">
-        <v>55925</v>
+        <v>7014</v>
       </c>
       <c r="AD6" t="n">
-        <v>3848</v>
+        <v>481</v>
       </c>
       <c r="AE6" t="inlineStr"/>
       <c r="AF6" t="inlineStr"/>
@@ -1260,25 +1260,25 @@
       <c r="A7" t="inlineStr"/>
       <c r="B7" t="inlineStr"/>
       <c r="C7" t="n">
-        <v>156</v>
+        <v>14</v>
       </c>
       <c r="D7" t="n">
-        <v>9839</v>
+        <v>5266</v>
       </c>
       <c r="E7" t="n">
-        <v>179935</v>
+        <v>58965</v>
       </c>
       <c r="F7" t="n">
-        <v>582199</v>
+        <v>118464</v>
       </c>
       <c r="G7" t="n">
-        <v>261962</v>
+        <v>78187</v>
       </c>
       <c r="H7" t="n">
-        <v>2877835</v>
+        <v>223975</v>
       </c>
       <c r="I7" t="n">
-        <v>166316</v>
+        <v>26062</v>
       </c>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
@@ -1298,22 +1298,22 @@
         <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>223</v>
+        <v>28</v>
       </c>
       <c r="Z7" t="n">
-        <v>6486</v>
+        <v>810</v>
       </c>
       <c r="AA7" t="n">
-        <v>237939</v>
+        <v>29968</v>
       </c>
       <c r="AB7" t="n">
-        <v>60821</v>
+        <v>7646</v>
       </c>
       <c r="AC7" t="n">
-        <v>3676427</v>
+        <v>460431</v>
       </c>
       <c r="AD7" t="n">
-        <v>96346</v>
+        <v>12050</v>
       </c>
       <c r="AE7" t="inlineStr"/>
       <c r="AF7" t="inlineStr"/>
@@ -1334,25 +1334,25 @@
       <c r="A8" t="inlineStr"/>
       <c r="B8" t="inlineStr"/>
       <c r="C8" t="n">
-        <v>295</v>
+        <v>13</v>
       </c>
       <c r="D8" t="n">
-        <v>273</v>
+        <v>96</v>
       </c>
       <c r="E8" t="n">
-        <v>13684</v>
+        <v>5682</v>
       </c>
       <c r="F8" t="n">
-        <v>33526</v>
+        <v>10771</v>
       </c>
       <c r="G8" t="n">
-        <v>22349</v>
+        <v>9332</v>
       </c>
       <c r="H8" t="n">
-        <v>343542</v>
+        <v>80714</v>
       </c>
       <c r="I8" t="n">
-        <v>1133453</v>
+        <v>86982</v>
       </c>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
@@ -1372,22 +1372,22 @@
         <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>224</v>
+        <v>28</v>
       </c>
       <c r="Z8" t="n">
-        <v>648</v>
+        <v>81</v>
       </c>
       <c r="AA8" t="n">
-        <v>2648</v>
+        <v>333</v>
       </c>
       <c r="AB8" t="n">
-        <v>2126</v>
+        <v>267</v>
       </c>
       <c r="AC8" t="n">
-        <v>100723</v>
+        <v>12636</v>
       </c>
       <c r="AD8" t="n">
-        <v>1440753</v>
+        <v>180245</v>
       </c>
       <c r="AE8" t="inlineStr"/>
       <c r="AF8" t="inlineStr"/>
